--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Extinto</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>S/N</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -29789,17 +29789,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>16613750.86</t>
+          <t>17794502.86</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>246679.7</t>
+          <t>307751.78</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>7793329.64</t>
+          <t>6612577.64</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30099,17 +30099,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>1170016</t>
+          <t>1721132.98</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>98632.72</t>
+          <t>145444.43</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>7572896.96</t>
+          <t>7021779.98</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -30409,17 +30409,17 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>16864716.77</t>
+          <t>19307497.15</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>406450.41</t>
+          <t>471877.41</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>13887226.82</t>
+          <t>11444446.44</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30595,17 +30595,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>6271540.57</t>
+          <t>6273968.77</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>190178.79</t>
+          <t>190232.93</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>5298365.38</t>
+          <t>5295937.18</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -31153,17 +31153,17 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>4689306.05</t>
+          <t>4882646.13</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>4266.85</t>
+          <t>5782.7</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>1289693.94</t>
+          <t>1096353.86</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -31339,17 +31339,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>5493423.52</t>
+          <t>9406237.44</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>118135.92</t>
+          <t>228279.24</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>40866487.81</t>
+          <t>36953673.89</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>3749064.97</t>
+          <t>4369741.51</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>19662830.23</t>
+          <t>19042153.69</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -35741,17 +35741,17 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>29468214.18</t>
+          <t>30564192.02</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>1364900.9</t>
+          <t>1457301.84</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>4358662.87</t>
+          <t>3262685.03</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -37291,17 +37291,17 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>33898181.2</t>
+          <t>36396906.94</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>1515085.1</t>
+          <t>1673775.08</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>13658609.06</t>
+          <t>11159883.32</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -37353,17 +37353,17 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>26214961.73</t>
+          <t>26841194.41</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>1261297.08</t>
+          <t>1305577.72</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>20790608.82</t>
+          <t>20164376.14</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -37477,17 +37477,17 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>28183468.37</t>
+          <t>29298676.25</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>1425134.61</t>
+          <t>1501609.19</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>21878585.91</t>
+          <t>20763378.03</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -37539,17 +37539,17 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>28269743.87</t>
+          <t>30478228.7</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>1193907.62</t>
+          <t>1352975.3</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>20861977.38</t>
+          <t>18653492.55</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
@@ -39399,17 +39399,17 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>4071228.78</t>
+          <t>4523545.91</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>146736.4</t>
+          <t>198715.79</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>705752.8</t>
+          <t>253435.67</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
@@ -39957,17 +39957,17 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>6596838.39</t>
+          <t>8408554.42</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>65380.93</t>
+          <t>101522.2</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>42496701.06</t>
+          <t>40684985.03</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -40143,17 +40143,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>3896181.61</t>
+          <t>4387192.4</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>76548.09</t>
+          <t>89921.22</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>5626810.68</t>
+          <t>5135799.89</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -40577,17 +40577,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>607490.03</t>
+          <t>641943.91</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>16508.38</t>
+          <t>17752.16</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>1048183.19</t>
+          <t>1013729.31</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -40817,17 +40817,17 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>5686230.5</t>
+          <t>9046120.89</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>593908.91</t>
+          <t>909138.31</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>9018666.41</t>
+          <t>5658776.02</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
@@ -41065,17 +41065,17 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>2952899.09</t>
+          <t>3799798.64</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>286623.48</t>
+          <t>396988.46</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>11764302.89</t>
+          <t>10917403.34</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
@@ -41189,17 +41189,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>5658949.14</t>
+          <t>6357335.88</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>502342.37</t>
+          <t>585658.12</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>6500324.69</t>
+          <t>5801937.95</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -41313,17 +41313,17 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>2605666.71</t>
+          <t>3855590.65</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>80545.16</t>
+          <t>105736.09</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>54861937.04</t>
+          <t>53612013.1</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
@@ -41437,17 +41437,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>651822.35</t>
+          <t>819736.1</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>20793.12</t>
+          <t>26149.56</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>2376226.61</t>
+          <t>2208312.86</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -41871,17 +41871,17 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>478830.48</t>
+          <t>630857.79</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>15274.67</t>
+          <t>20124.34</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>2708708.68</t>
+          <t>2556681.37</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
@@ -42119,17 +42119,17 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>646153.82</t>
+          <t>832509.47</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>20612.29</t>
+          <t>26557.03</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>6031250.51</t>
+          <t>5844894.86</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
@@ -42181,17 +42181,17 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>82269.93</t>
+          <t>150647.81</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>6584.71</t>
+          <t>8654.61</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>10537548.9</t>
+          <t>10469171.02</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -42367,17 +42367,17 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>2214018.44</t>
+          <t>2959871.86</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>281482.05</t>
+          <t>372766.6</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>12184027.63</t>
+          <t>11438174.21</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
@@ -42491,17 +42491,17 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>135793.06</t>
+          <t>659585.43</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>12064.42</t>
+          <t>40934.27</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>2826904.7</t>
+          <t>2303112.33</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -42615,7 +42615,7 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>754828.33</t>
+          <t>2386447.73</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -42625,7 +42625,7 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>19043171.67</t>
+          <t>17411552.27</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
@@ -43359,17 +43359,17 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>515868.33</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4910.81</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>4005503.13</t>
+          <t>3489634.8</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
@@ -43421,17 +43421,17 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>703941.21</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12621.94</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>2520936.14</t>
+          <t>1816994.93</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -43483,17 +43483,17 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318231.68</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4229.76</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>3287560.73</t>
+          <t>2969329.05</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -43669,17 +43669,17 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>1030693.14</t>
+          <t>6526131.17</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>115066.24</t>
+          <t>546920.45</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>35919823.46</t>
+          <t>30424385.43</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
@@ -44227,17 +44227,17 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2110592.91</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336564.06</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>39537597.48</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
@@ -44351,17 +44351,17 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>18528625.14</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
@@ -44438,7 +44438,11 @@
           <t>DC-9501894/2026</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>9501894</t>
+        </is>
+      </c>
       <c r="C711" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44484,7 +44488,11 @@
           <t>4742883</t>
         </is>
       </c>
-      <c r="L711" t="inlineStr"/>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>2301520 000042/2025</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -44715,17 +44723,17 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>159783.86</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>5097.09</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>31540215.1</t>
+          <t>31475050.39</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -44777,17 +44785,17 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>167906.5</t>
+          <t>236383.87</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>5356.2</t>
+          <t>7540.62</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>35822091.63</t>
+          <t>35753614.26</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
@@ -45087,17 +45095,17 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>2434106.96</t>
+          <t>3119625.83</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>289651.76</t>
+          <t>404393.35</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>30669944.94</t>
+          <t>29984426.07</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
@@ -45112,7 +45120,11 @@
           <t>DC-9518766/2026</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr"/>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>9518766</t>
+        </is>
+      </c>
       <c r="C722" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45158,7 +45170,11 @@
           <t>120800000</t>
         </is>
       </c>
-      <c r="L722" t="inlineStr"/>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2301520 000047/2025</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -45203,7 +45219,7 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1063647.94</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
@@ -45213,7 +45229,7 @@
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>13061350.45</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
@@ -45443,17 +45459,17 @@
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>138602.75</t>
+          <t>195614.89</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>4421.42</t>
+          <t>6240.1</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>77760291.55</t>
+          <t>77703279.41</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -30275,12 +30275,12 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243556.56</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>7109673.15</t>
+          <t>7353229.71</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30295,7 +30295,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>2083846.55</t>
+          <t>2327403.11</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30399,12 +30399,12 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>5770491.09</t>
+          <t>5878145.36</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>30751943.59</t>
+          <t>30859597.86</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>11444446.44</t>
+          <t>11552100.71</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -31143,12 +31143,12 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1109689.6</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>5978999.99</t>
+          <t>7088689.59</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -31163,7 +31163,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>1096353.86</t>
+          <t>2206043.46</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -31835,17 +31835,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>1499335.05</t>
+          <t>1778112.36</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>47119.06</t>
+          <t>57182.91</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>7911010.84</t>
+          <t>7632233.53</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -32455,17 +32455,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>806267.63</t>
+          <t>859179.66</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>91155.09</t>
+          <t>99308.83</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>324849.43</t>
+          <t>271937.4</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -32641,17 +32641,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>1394881.54</t>
+          <t>1510488.25</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>152486.62</t>
+          <t>170301.61</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>326071.97</t>
+          <t>210465.26</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -37973,17 +37973,17 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>47974122.69</t>
+          <t>48413382.73</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>1540779.52</t>
+          <t>1581008.74</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>13847350.52</t>
+          <t>13408090.48</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -38769,12 +38769,12 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>855065.31</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>4917800.43</t>
+          <t>5772865.74</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>2264466.06</t>
+          <t>3119531.37</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -39089,17 +39089,17 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>27988715.04</t>
+          <t>28613244.68</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>356282.35</t>
+          <t>370367.84</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>3659289.31</t>
+          <t>3034759.67</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
@@ -39275,17 +39275,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>2371518.36</t>
+          <t>2227471.49</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>106638.79</t>
+          <t>97506.22</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>3403234.08</t>
+          <t>3547280.95</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -41737,12 +41737,12 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4705677.57</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>41984578.11</t>
+          <t>46690255.68</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41757,7 +41757,7 @@
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>11245998</t>
+          <t>15951675.57</t>
         </is>
       </c>
       <c r="L667" t="inlineStr">
@@ -41995,17 +41995,17 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>2857130.14</t>
+          <t>4464375.13</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>68579.53</t>
+          <t>106824.54</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>18630408.65</t>
+          <t>17023163.66</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -42057,17 +42057,17 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>1777707.89</t>
+          <t>2669790.98</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>75112.42</t>
+          <t>108153.33</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>58112291.69</t>
+          <t>57220208.6</t>
         </is>
       </c>
       <c r="L672" t="inlineStr">
@@ -42481,12 +42481,12 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>712081.68</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>2962697.76</t>
+          <t>3674779.44</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -42501,7 +42501,7 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>2303112.33</t>
+          <t>3015194.01</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -45033,17 +45033,17 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>485014.38</t>
+          <t>1651439.99</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>33558.09</t>
+          <t>86138.13</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>13779736.44</t>
+          <t>12613310.83</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L732"/>
+  <dimension ref="A1:L739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Extinto</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17025,17 +17025,17 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>20427521.85</t>
+          <t>20445812.21</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>2074335.86</t>
+          <t>2077154.4</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>4437992.18</t>
+          <t>4419701.82</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Registro de Preços</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>S/N</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -30719,17 +30719,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>5503746.21</t>
+          <t>6052903.76</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>154307.98</t>
+          <t>174132.56</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>25368326.09</t>
+          <t>24819168.54</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>5087668.17</t>
+          <t>5129405.67</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>4797562.65</t>
+          <t>4755825.15</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -39523,17 +39523,17 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>209714.4</t>
+          <t>239548.02</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>11180.21</t>
+          <t>13393.86</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1136632.06</t>
+          <t>1106798.44</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -41003,17 +41003,17 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>4842504.05</t>
+          <t>5685541.39</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>1033446.24</t>
+          <t>1213361.64</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>17325326.42</t>
+          <t>16482289.08</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -41127,17 +41127,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>4799556.95</t>
+          <t>5606299.71</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>1022765.69</t>
+          <t>1194687.15</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>23194826.08</t>
+          <t>22388083.32</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -41375,17 +41375,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>1624332.96</t>
+          <t>1843076.47</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>348817.13</t>
+          <t>395809.96</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>13305013.99</t>
+          <t>13086270.48</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>2366973.95</t>
+          <t>3674234.5</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>504865.43</t>
+          <t>783693.91</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>22125749.21</t>
+          <t>20818488.66</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41809,17 +41809,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>1051785.7</t>
+          <t>1620130.93</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>222978.39</t>
+          <t>343467.5</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>8254844.5</t>
+          <t>7686499.27</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -42702,11 +42702,7 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>9512044</t>
-        </is>
-      </c>
+      <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -42752,11 +42748,7 @@
           <t>11358610.11</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>2301762 000001/2026</t>
-        </is>
-      </c>
+      <c r="L683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -43235,7 +43227,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>249842.9</t>
+          <t>407304.69</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -43245,7 +43237,7 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>5092739.98</t>
+          <t>4935278.19</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -43607,17 +43599,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>336759.53</t>
+          <t>545858.7</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>183730.69</t>
+          <t>302080.82</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>4169958.53</t>
+          <t>3960859.36</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -43818,11 +43810,7 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
+      <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -43868,11 +43856,7 @@
           <t>7919248.4</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr">
-        <is>
-          <t>2301520 000001/2026</t>
-        </is>
-      </c>
+      <c r="L701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -43880,11 +43864,7 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
+      <c r="B702" t="inlineStr"/>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43930,11 +43910,7 @@
           <t>4277399.55</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr">
-        <is>
-          <t>2301520 000001/2026</t>
-        </is>
-      </c>
+      <c r="L702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -43942,11 +43918,7 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -43992,11 +43964,7 @@
           <t>3773464.12</t>
         </is>
       </c>
-      <c r="L703" t="inlineStr">
-        <is>
-          <t>2301520 000001/2026</t>
-        </is>
-      </c>
+      <c r="L703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -44004,11 +43972,7 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -44054,23 +44018,15 @@
           <t>209886.65</t>
         </is>
       </c>
-      <c r="L704" t="inlineStr">
-        <is>
-          <t>2301520 000001/2026</t>
-        </is>
-      </c>
+      <c r="L704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
-        </is>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>9493529</t>
-        </is>
-      </c>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44078,17 +44034,17 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>Recuperação Funcional MGC-259, Guanhães - Sabinópolis e Sabinópolis - Serro; AMG-0810, Serro - Alvorada de Minas</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>37600000</t>
+          <t>46639997.64</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -44098,7 +44054,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>37600000</t>
+          <t>46639997.64</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -44113,44 +44069,36 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>37600000</t>
-        </is>
-      </c>
-      <c r="L705" t="inlineStr">
-        <is>
-          <t>2301520 000036/2025</t>
-        </is>
-      </c>
+          <t>46639997.64</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>9275590</t>
-        </is>
-      </c>
+          <t>DC-9519020/2026</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr"/>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>Restauração do Trecho: Timóteo - Entrº LMG-760 (Cava Grande), na rodovia MG425, com 8,000 km de extensão.</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>7088404.99</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -44160,39 +44108,35 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>7088404.99</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>175646.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>58016.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>924077.81</t>
-        </is>
-      </c>
-      <c r="L706" t="inlineStr">
-        <is>
-          <t>2301901 000003/2021</t>
-        </is>
-      </c>
+          <t>7088404.99</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -44202,17 +44146,17 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -44222,59 +44166,55 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>2110592.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>336564.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>39537597.48</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
-        </is>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>9507997</t>
-        </is>
-      </c>
+          <t>DC-9519017/2026</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Ponte sobre o Ribeirão Mata Boi na Rodovia MG-414, trecho Araguari (Distrito de Amanhece) - Divisa MG/GO, com 50,000 m de extensão</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>5995000</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -44284,7 +44224,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>5995000</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44299,44 +44239,40 @@
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>9289765.74</t>
-        </is>
-      </c>
-      <c r="L708" t="inlineStr">
-        <is>
-          <t>1301606 000002/2026</t>
-        </is>
-      </c>
+          <t>5995000</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44346,59 +44282,55 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>386354.63</t>
+          <t>175646.62</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>69710.13</t>
+          <t>58016.06</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>18528625.14</t>
+          <t>924077.81</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>9515457</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr"/>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44408,59 +44340,55 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2110592.91</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336564.06</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L710" t="inlineStr">
-        <is>
-          <t>2301520 000005/2026</t>
-        </is>
-      </c>
+          <t>39537597.48</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44470,7 +44398,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44485,24 +44413,24 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44517,12 +44445,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44532,7 +44460,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44547,24 +44475,24 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44579,12 +44507,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44594,39 +44522,39 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18528625.14</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44636,17 +44564,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44656,59 +44584,55 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>167084.18</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>5329.96</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>47182914.25</t>
+          <t>18528625.14</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>9493205</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44718,41 +44642,33 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>31475050.39</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>26137308.02</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>9482032</t>
-        </is>
-      </c>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
       <c r="C716" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44760,17 +44676,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44780,59 +44696,51 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>236383.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>7540.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>35753614.26</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>4742883</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>9481987</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44842,41 +44750,33 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>594602.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>18967.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>22840396.96</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>36643741.73</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>9482055</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44884,17 +44784,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44904,39 +44804,35 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>31997186.78</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>25215151.46</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44946,17 +44842,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44966,39 +44862,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235226.18</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7503.68</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47114772.25</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -45008,17 +44904,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45028,39 +44924,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>1651439.99</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>86138.13</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>12613310.83</t>
+          <t>31475050.39</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45070,59 +44966,59 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>3119625.83</t>
+          <t>236383.87</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>404393.35</t>
+          <t>7540.62</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>29984426.07</t>
+          <t>35753614.26</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45132,17 +45028,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45152,39 +45048,39 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012281.35</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32291.76</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>22422718.45</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45194,17 +45090,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45214,37 +45110,41 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>1063647.94</t>
+          <t>138214.93</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4409.04</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>13061350.45</t>
+          <t>31959785.03</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C724" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45257,12 +45157,12 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45272,12 +45172,12 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>180823.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
@@ -45287,10 +45187,14 @@
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>1587518.91</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -45310,42 +45214,42 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>883000.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>28167.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>36281731.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
@@ -45357,12 +45261,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45372,17 +45276,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45392,39 +45296,39 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1651439.99</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86138.13</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>12613310.83</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45434,61 +45338,57 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>3119625.83</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>404393.35</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>77703279.41</t>
+          <t>29984426.07</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>9512043</t>
-        </is>
-      </c>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45496,17 +45396,17 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45516,7 +45416,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45531,26 +45431,18 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>44002130</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
-        <is>
-          <t>2301762 000004/2026</t>
-        </is>
-      </c>
+          <t>120800000</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr"/>
       <c r="C729" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45558,17 +45450,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45578,41 +45470,33 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>1549222.57</t>
+          <t>1063647.94</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>209376.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>23283240.64</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>13061350.45</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45620,17 +45504,17 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45640,39 +45524,35 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>2345896.62</t>
+          <t>180823.74</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>337318.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>32076181.73</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>1587518.91</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -45682,107 +45562,533 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>2410184.11</t>
+          <t>883000.37</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>274971.65</t>
+          <t>28167.69</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>28193013.76</t>
+          <t>36281731.86</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>195614.89</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>6240.1</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>77703279.41</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr"/>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>1549222.57</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>209376.64</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>23283240.64</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>2345896.62</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>337318.43</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>32076181.73</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>2410184.11</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>274971.65</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>28193013.76</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
+      <c r="B739" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D732" t="inlineStr">
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E732" t="inlineStr">
+      <c r="E739" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F732" t="inlineStr">
+      <c r="F739" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H732" t="inlineStr">
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I732" t="inlineStr">
+      <c r="I739" t="inlineStr">
         <is>
           <t>4215392.16</t>
         </is>
       </c>
-      <c r="J732" t="inlineStr">
+      <c r="J739" t="inlineStr">
         <is>
           <t>531866.62</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr">
+      <c r="K739" t="inlineStr">
         <is>
           <t>26957142.42</t>
         </is>
       </c>
-      <c r="L732" t="inlineStr">
+      <c r="L739" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L739"/>
+  <dimension ref="A1:L755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>PRC-29.007/2017-B</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-010/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Extinto</t>
+          <t>DC-008/2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-22.016/2020</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-22.016/2020</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-003/2021</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27406,7 +27406,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27778,7 +27778,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -39426,7 +39426,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -39736,7 +39736,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -42702,7 +42702,11 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr"/>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
       <c r="C683" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43810,7 +43814,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C701" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -43864,7 +43872,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43918,7 +43930,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -43972,7 +43988,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C704" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -44026,7 +44046,11 @@
           <t>DM-9519034/2026</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
       <c r="C705" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44080,7 +44104,11 @@
           <t>DC-9519020/2026</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>9519020</t>
+        </is>
+      </c>
       <c r="C706" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44196,7 +44224,11 @@
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
       <c r="C708" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44312,7 +44344,11 @@
           <t>DM-007/2024-A</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr"/>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
       <c r="C710" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44497,7 +44533,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -44507,12 +44543,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44522,22 +44558,22 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>386354.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>69710.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>18528625.14</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -44559,7 +44595,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -44569,12 +44605,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44584,22 +44620,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>386354.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>69710.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>18528625.14</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44611,13 +44647,17 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -44627,12 +44667,12 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44642,33 +44682,41 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr"/>
+          <t>18528625.14</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C716" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44676,17 +44724,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44696,36 +44744,44 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>4742883</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr"/>
+          <t>18528625.14</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -44735,12 +44791,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44750,33 +44806,41 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>36643741.73</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
+          <t>18528625.14</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C718" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44789,12 +44853,12 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44804,55 +44868,59 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386354.63</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69710.13</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>25215151.46</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr"/>
+          <t>18528625.14</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44862,39 +44930,35 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>235226.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>7503.68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>47114772.25</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>26137308.02</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44904,17 +44968,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44924,59 +44988,55 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>31475050.39</t>
-        </is>
-      </c>
-      <c r="L720" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>4742883</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -44986,39 +45046,35 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>236383.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>7540.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>35753614.26</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>36643741.73</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45028,17 +45084,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45048,39 +45104,35 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>1012281.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>32291.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>22422718.45</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>25215151.46</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45095,12 +45147,12 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45110,22 +45162,22 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>138214.93</t>
+          <t>235226.18</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>4409.04</t>
+          <t>7503.68</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>31959785.03</t>
+          <t>47114772.25</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
@@ -45137,12 +45189,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45152,17 +45204,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45172,39 +45224,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31475050.39</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45214,17 +45266,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45234,39 +45286,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236383.87</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7540.62</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35753614.26</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45276,17 +45328,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45296,39 +45348,39 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>1651439.99</t>
+          <t>1012281.35</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>86138.13</t>
+          <t>32291.76</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>12613310.83</t>
+          <t>22422718.45</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45338,57 +45390,61 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>3119625.83</t>
+          <t>138214.93</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>404393.35</t>
+          <t>4409.04</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>29984426.07</t>
+          <t>31959785.03</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C728" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45401,12 +45457,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45416,7 +45472,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45431,18 +45487,26 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>120800000</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C729" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45450,17 +45514,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45470,12 +45534,12 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>1063647.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -45485,18 +45549,26 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>13061350.45</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C730" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45509,12 +45581,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45524,12 +45596,12 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>180823.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
@@ -45539,10 +45611,14 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>1587518.91</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -45562,42 +45638,42 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>883000.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>28167.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>36281731.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
@@ -45624,42 +45700,42 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>883000.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>28167.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>36281731.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
@@ -45671,12 +45747,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45686,17 +45762,17 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -45706,7 +45782,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45721,24 +45797,24 @@
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -45748,17 +45824,17 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45768,37 +45844,41 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>77703279.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C735" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45806,17 +45886,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45826,7 +45906,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45841,20 +45921,24 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>44002130</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -45864,17 +45948,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -45884,39 +45968,39 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>1549222.57</t>
+          <t>1651439.99</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>209376.64</t>
+          <t>86138.13</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>23283240.64</t>
+          <t>12613310.83</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -45931,37 +46015,37 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>2345896.62</t>
+          <t>3119625.83</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>337318.43</t>
+          <t>404393.35</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>32076181.73</t>
+          <t>29984426.07</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
@@ -45973,12 +46057,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -45988,17 +46072,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -46008,87 +46092,1059 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>2410184.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>274971.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>28193013.76</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>120800000</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>1063647.94</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>13061350.45</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>180823.74</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>1587518.91</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>883000.37</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>28167.69</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>36281731.86</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>195614.89</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>6240.1</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>77703279.41</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>1549222.57</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>209376.64</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>23283240.64</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>2345896.62</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>337318.43</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>32076181.73</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>2410184.11</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>274971.65</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>28193013.76</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B755" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D739" t="inlineStr">
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr">
+      <c r="E755" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F739" t="inlineStr">
+      <c r="F755" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H739" t="inlineStr">
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I739" t="inlineStr">
+      <c r="I755" t="inlineStr">
         <is>
           <t>4215392.16</t>
         </is>
       </c>
-      <c r="J739" t="inlineStr">
+      <c r="J755" t="inlineStr">
         <is>
           <t>531866.62</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr">
+      <c r="K755" t="inlineStr">
         <is>
           <t>26957142.42</t>
         </is>
       </c>
-      <c r="L739" t="inlineStr">
+      <c r="L755" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L740"/>
+  <dimension ref="A1:L748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44419,7 +44419,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -44429,12 +44429,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44444,22 +44444,22 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -44481,7 +44481,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -44491,12 +44491,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44506,22 +44506,22 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -44533,13 +44533,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -44549,12 +44553,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44564,33 +44568,41 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C715" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44598,17 +44610,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44618,36 +44630,44 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>52753.74</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>1946.61</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>4690129.26</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -44657,12 +44677,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44672,33 +44692,41 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C717" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44711,12 +44739,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44726,55 +44754,55 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>9482017</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44784,41 +44812,33 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>312620.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>9972.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>47037378.35</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>26137308.02</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>9493205</t>
-        </is>
-      </c>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44826,17 +44846,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44846,55 +44866,51 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>52753.74</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>1946.61</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>31475050.39</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>4690129.26</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44904,22 +44920,22 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>236383.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>7540.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>35753614.26</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="L720" t="inlineStr"/>
@@ -44927,14 +44943,10 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>9481987</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44942,17 +44954,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -44962,39 +44974,35 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>1012281.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>32291.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>22422718.45</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>25215151.46</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45009,12 +45017,12 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45024,22 +45032,22 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>210748.49</t>
+          <t>312620.08</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>6761.64</t>
+          <t>9972.54</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>31887251.47</t>
+          <t>47037378.35</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -45051,12 +45059,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45066,17 +45074,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45086,41 +45094,37 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31475050.39</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DO-009482032/2025-L6</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45128,17 +45132,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45148,37 +45152,37 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236383.87</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7540.62</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>35753614.26</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr"/>
+          <t>DO-9481987/2025-L7</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>9481987</t>
+        </is>
+      </c>
       <c r="C725" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45186,17 +45190,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45206,35 +45210,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012281.35</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32291.76</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr"/>
+          <t>22422718.45</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45244,17 +45252,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45264,39 +45272,39 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>6418794.48</t>
+          <t>210748.49</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>293904.2</t>
+          <t>6761.64</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>7845956.34</t>
+          <t>31887251.47</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45306,57 +45314,61 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>3582262.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>483231.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>29521789.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C728" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45369,12 +45381,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45384,12 +45396,12 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>2633312.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -45399,18 +45411,26 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>118166687.04</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C729" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45418,17 +45438,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45438,12 +45458,12 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>1750547.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -45453,18 +45473,26 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>12374450.41</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C730" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45477,12 +45505,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45492,12 +45520,12 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>271235.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
@@ -45507,22 +45535,22 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>1497107.03</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DC-9519595/2026</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr"/>
       <c r="C731" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45530,59 +45558,55 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>35817138.14</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>69497864.4</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -45592,59 +45616,59 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>6418794.48</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>293904.2</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>7845956.34</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45654,61 +45678,57 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3582262.51</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483231.71</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>29521789.39</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr"/>
       <c r="C734" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45716,17 +45736,17 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45736,34 +45756,30 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>2633312.96</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>77703279.41</t>
-        </is>
-      </c>
-      <c r="L734" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>118166687.04</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B735" t="inlineStr"/>
@@ -45774,17 +45790,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45794,12 +45810,12 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>1334144.24</t>
+          <t>1750547.98</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -45809,7 +45825,7 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>42667985.76</t>
+          <t>12374450.41</t>
         </is>
       </c>
       <c r="L735" t="inlineStr"/>
@@ -45817,7 +45833,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
         </is>
       </c>
       <c r="B736" t="inlineStr"/>
@@ -45833,12 +45849,12 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -45848,12 +45864,12 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271235.62</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -45863,7 +45879,7 @@
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>1497107.03</t>
         </is>
       </c>
       <c r="L736" t="inlineStr"/>
@@ -45871,12 +45887,12 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -45886,59 +45902,59 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>2061135.63</t>
+          <t>1347594.09</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>294133.25</t>
+          <t>42988.22</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>22771327.58</t>
+          <t>35817138.14</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -45948,59 +45964,59 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>3070543.84</t>
+          <t>1347594.09</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>453610.76</t>
+          <t>42988.22</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>31351534.51</t>
+          <t>35817138.14</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -46010,107 +46026,587 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>2983913.41</t>
+          <t>1347594.09</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>354928.45</t>
+          <t>42988.22</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>27619284.46</t>
+          <t>35817138.14</t>
         </is>
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>195614.89</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>6240.1</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>77703279.41</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr"/>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>1334144.24</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>42667985.76</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr"/>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>2061135.63</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>294133.25</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>22771327.58</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>3070543.84</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>453610.76</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>31351534.51</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>2983913.41</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>354928.45</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>27619284.46</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B740" t="inlineStr">
+      <c r="B748" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D740" t="inlineStr">
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E740" t="inlineStr">
+      <c r="E748" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F740" t="inlineStr">
+      <c r="F748" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G740" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H740" t="inlineStr">
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I740" t="inlineStr">
+      <c r="I748" t="inlineStr">
         <is>
           <t>4953312.78</t>
         </is>
       </c>
-      <c r="J740" t="inlineStr">
+      <c r="J748" t="inlineStr">
         <is>
           <t>634447.12</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr">
+      <c r="K748" t="inlineStr">
         <is>
           <t>26219221.8</t>
         </is>
       </c>
-      <c r="L740" t="inlineStr">
+      <c r="L748" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L748"/>
+  <dimension ref="A1:L780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42516,7 +42516,11 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr"/>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
       <c r="C680" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43624,7 +43628,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C698" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -43678,7 +43686,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C699" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43732,7 +43744,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C700" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -43786,7 +43802,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C701" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -43840,7 +43860,11 @@
           <t>DM-9519034/2026</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43894,7 +43918,11 @@
           <t>DC-9519020/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9519020</t>
+        </is>
+      </c>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44010,7 +44038,11 @@
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
       <c r="C705" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44064,7 +44096,11 @@
           <t>DC-9519295/2026</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C706" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44118,7 +44154,11 @@
           <t>DC-9518140/2026</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
       <c r="C707" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44234,7 +44274,11 @@
           <t>DM-007/2024-A</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>9422060</t>
+        </is>
+      </c>
       <c r="C709" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44543,7 +44587,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -44553,12 +44597,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44568,22 +44612,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44605,7 +44649,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -44615,12 +44659,12 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44630,22 +44674,22 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -44667,7 +44711,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -44677,12 +44721,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44692,22 +44736,22 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
@@ -44729,7 +44773,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -44739,12 +44783,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44754,22 +44798,22 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
@@ -44781,13 +44825,17 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -44797,12 +44845,12 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44812,33 +44860,41 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C719" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44846,17 +44902,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44866,36 +44922,44 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>52753.74</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>1946.61</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>4690129.26</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -44905,12 +44969,12 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44920,33 +44984,41 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
-        </is>
-      </c>
-      <c r="L720" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B721" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C721" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44959,12 +45031,12 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -44974,35 +45046,39 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45012,17 +45088,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45032,39 +45108,39 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>312620.08</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>9972.54</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>47037378.35</t>
+          <t>18527912.34</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45074,17 +45150,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45094,37 +45170,41 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>31475050.39</t>
+          <t>18527912.34</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C724" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45132,17 +45212,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45152,35 +45232,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>236383.87</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>7540.62</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>35753614.26</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45190,17 +45274,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45210,59 +45294,59 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>1012281.35</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>32291.76</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>22422718.45</t>
+          <t>18527912.34</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45272,39 +45356,35 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>210748.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>6761.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>31887251.47</t>
-        </is>
-      </c>
-      <c r="L726" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>26137308.02</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45314,17 +45394,17 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -45334,44 +45414,40 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52753.74</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1946.61</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>4690129.26</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -45381,12 +45457,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45396,7 +45472,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45411,24 +45487,20 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>36643741.73</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -45443,12 +45515,12 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45458,7 +45530,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45473,24 +45545,20 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>25215151.46</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -45500,17 +45568,17 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45520,37 +45588,41 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312620.08</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9972.54</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47037378.35</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr"/>
+          <t>DO-9493205/2026-L4</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>9493205</t>
+        </is>
+      </c>
       <c r="C731" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45558,17 +45630,17 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -45578,35 +45650,39 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>69497864.4</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr"/>
+          <t>31475050.39</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -45616,17 +45692,17 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -45636,39 +45712,35 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>6418794.48</t>
+          <t>236383.87</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>293904.2</t>
+          <t>7540.62</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>7845956.34</t>
-        </is>
-      </c>
-      <c r="L732" t="inlineStr">
-        <is>
-          <t>2301762 000023/2025</t>
-        </is>
-      </c>
+          <t>35753614.26</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45678,57 +45750,61 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>3582262.51</t>
+          <t>1012281.35</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>483231.71</t>
+          <t>32291.76</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>29521789.39</t>
+          <t>22422718.45</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr"/>
+          <t>DO-009482055/2025-L5</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>9482055</t>
+        </is>
+      </c>
       <c r="C734" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45736,17 +45812,17 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45756,33 +45832,41 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>2633312.96</t>
+          <t>210748.49</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6761.64</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>118166687.04</t>
-        </is>
-      </c>
-      <c r="L734" t="inlineStr"/>
+          <t>31887251.47</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C735" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45790,17 +45874,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45810,12 +45894,12 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>1750547.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
@@ -45825,18 +45909,26 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>12374450.41</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C736" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45849,12 +45941,12 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -45864,12 +45956,12 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>271235.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -45879,10 +45971,14 @@
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>1497107.03</t>
-        </is>
-      </c>
-      <c r="L736" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -45902,42 +45998,42 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
@@ -45964,42 +46060,42 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
@@ -46026,42 +46122,42 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L739" t="inlineStr">
@@ -46088,42 +46184,42 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
@@ -46135,12 +46231,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -46150,17 +46246,17 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -46170,7 +46266,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -46185,24 +46281,24 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -46212,17 +46308,17 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -46232,37 +46328,41 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>77703279.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C743" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -46270,17 +46370,17 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -46290,12 +46390,12 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>1334144.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -46305,18 +46405,26 @@
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>42667985.76</t>
-        </is>
-      </c>
-      <c r="L743" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B744" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C744" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -46329,12 +46437,12 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -46344,7 +46452,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -46359,20 +46467,24 @@
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>61779996.11</t>
-        </is>
-      </c>
-      <c r="L744" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -46382,17 +46494,17 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -46402,39 +46514,39 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>2061135.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>294133.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>22771327.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -46444,17 +46556,17 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -46464,39 +46576,39 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>3070543.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>453610.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>31351534.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -46506,17 +46618,17 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -46526,87 +46638,2043 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>2983913.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>354928.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>27619284.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>DC-9519595/2026</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>9519595</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>69497864.4</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>69497864.4</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>69497864.4</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>9497685</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>14264750.82</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>14264750.82</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>6418794.48</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>293904.2</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>7845956.34</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>2301762 000023/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>9414460</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>32998445.8</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>105606.1</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>33104051.9</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>3582262.51</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>483231.71</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>29521789.39</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>9518766</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>120800000</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>120800000</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>2633312.96</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>118166687.04</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>1750547.98</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>12374450.41</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr"/>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>271235.62</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>1497107.03</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>195614.89</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>6240.1</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>77703279.41</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>1334144.24</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>42667985.76</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>2061135.63</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>294133.25</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>22771327.58</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>3070543.84</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>453610.76</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>31351534.51</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>2983913.41</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>354928.45</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>27619284.46</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B748" t="inlineStr">
+      <c r="B780" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D748" t="inlineStr">
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E748" t="inlineStr">
+      <c r="E780" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F748" t="inlineStr">
+      <c r="F780" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G748" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H748" t="inlineStr">
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I748" t="inlineStr">
+      <c r="I780" t="inlineStr">
         <is>
           <t>4953312.78</t>
         </is>
       </c>
-      <c r="J748" t="inlineStr">
+      <c r="J780" t="inlineStr">
         <is>
           <t>634447.12</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr">
+      <c r="K780" t="inlineStr">
         <is>
           <t>26219221.8</t>
         </is>
       </c>
-      <c r="L748" t="inlineStr">
+      <c r="L780" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>
